--- a/reports/tests/recovery_lock_runtime_case.xlsx
+++ b/reports/tests/recovery_lock_runtime_case.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="124">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -273,6 +273,21 @@
   </si>
   <si>
     <t xml:space="preserve">SmallPnL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CostMultiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpreadCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommissionCost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SwapCost</t>
   </si>
   <si>
     <t xml:space="preserve">Costs</t>
@@ -831,18 +846,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B2" s="0" t="str">
         <f aca="false">IF(OR(SectionCalculator_UP!B31&gt;0,SectionCalculator_UP!B32="NO"),"OK","ERROR")</f>
@@ -855,7 +870,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B3" s="0" t="str">
         <f aca="false">IF(OR(SectionCalculator_UP!B32="YES",TailRecovery_UP!B10=0),"OK","ERROR")</f>
@@ -868,7 +883,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">IF(TailRecovery_UP!B12&lt;=TailRecovery_UP!B7,"OK","ERROR")</f>
@@ -881,20 +896,20 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="0" t="e">
+        <v>122</v>
+      </c>
+      <c r="B5" s="0" t="str">
         <f aca="false">IF(OR(SectionCalculator_UP!B14="NO",SectionCalculator_UP!B12="YES"),"OK","ERROR")</f>
-        <v>#NAME?</v>
+        <v>OK</v>
       </c>
       <c r="C5" s="0" t="e">
         <f aca="false">IF(OR(SectionCalculator_DOWN!B14="NO",SectionCalculator_DOWN!B12="YES"),"OK","ERROR")</f>
-        <v>#NAME?</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">IF(SectionCalculator_UP!B13="YES","OK","ERROR")</f>
@@ -9673,7 +9688,7 @@
         <v>62</v>
       </c>
       <c r="B223" s="0" t="n">
-        <f aca="false">IF(B222="N/A",0,xlookup(B222,A7:A206,D7:D206,0))</f>
+        <f aca="false">IF(B222="N/A",0,INDEX(D7:D206,MATCH(B222,A7:A206,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -9682,7 +9697,7 @@
         <v>63</v>
       </c>
       <c r="B224" s="0" t="n">
-        <f aca="false">IF(B222="N/A",0,ABS(xlookup(B222,A7:A206,H7:H206,0)))</f>
+        <f aca="false">IF(B222="N/A",0,ABS(INDEX(H7:H206,MATCH(B222,A7:A206,0))))</f>
         <v>0</v>
       </c>
     </row>
@@ -18257,7 +18272,7 @@
         <v>62</v>
       </c>
       <c r="B223" s="0" t="n">
-        <f aca="false">IF(B222="N/A",0,xlookup(B222,A7:A206,D7:D206,0))</f>
+        <f aca="false">IF(B222="N/A",0,INDEX(D7:D206,MATCH(B222,A7:A206,0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -18266,7 +18281,7 @@
         <v>63</v>
       </c>
       <c r="B224" s="0" t="n">
-        <f aca="false">IF(B222="N/A",0,ABS(xlookup(B222,A7:A206,H7:H206,0)))</f>
+        <f aca="false">IF(B222="N/A",0,ABS(INDEX(H7:H206,MATCH(B222,A7:A206,0))))</f>
         <v>0</v>
       </c>
     </row>
@@ -18295,7 +18310,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18336,36 +18351,36 @@
       <c r="A5" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="0" t="e">
-        <f aca="false">xlookup(B4,Settings!A21:A24,Settings!B21:B24)</f>
-        <v>#NAME?</v>
+      <c r="B5" s="0" t="n">
+        <f aca="false">INDEX(Settings!B21:B24,MATCH(B4,Settings!A21:A24,0))</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="0" t="e">
-        <f aca="false">xlookup(B4,Settings!A21:A24,Settings!C21:C24)</f>
-        <v>#NAME?</v>
+      <c r="B6" s="0" t="n">
+        <f aca="false">INDEX(Settings!C21:C24,MATCH(B4,Settings!A21:A24,0))</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="0" t="e">
+      <c r="B7" s="0" t="n">
         <f aca="false">FLOOR(B3*B5,Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="0" t="e">
+      <c r="B8" s="0" t="n">
         <f aca="false">FLOOR(B3*B6,Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18381,45 +18396,43 @@
       <c r="A10" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="0" t="e">
+      <c r="B10" s="0" t="n">
         <f aca="false">SUM(CurrentPositions!D2:D500)+B7+B8</f>
-        <v>#NAME?</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="0" t="e">
+      <c r="B11" s="0" t="n">
         <f aca="false">ABS(SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"BUY")+IF(B2="BUY",B7,0)+IF(B2="SELL",B8,0)-SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"SELL")-IF(B2="SELL",B7,0)-IF(B2="BUY",B8,0))</f>
-        <v>#NAME?</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="0" t="e">
-        <f aca="false">IF(Scenario_UP!B4&gt;=INDEX(Scenario_UP!E4:E7,B4),"YES","NO")</f>
-        <v>#VALUE!</v>
+      <c r="B12" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="0" t="str">
-        <f aca="false">IF(B2="SELL",IF(COUNTIFS(CurrentPositions!B2:B500,"BUY",CurrentPositions!C2:C500,"SECTION_BIG")=0,"YES","NO"),IF(B2="BUY",IF(COUNTIFS(CurrentPositions!B2:B500,"SELL",CurrentPositions!C2:C500,"SECTION_BIG")=0,"YES","NO"),"NO"))</f>
-        <v>YES</v>
+      <c r="B13" s="0" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="0" t="e">
+      <c r="B14" s="0" t="str">
         <f aca="false">IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO")</f>
-        <v>#NAME?</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18467,6 +18480,21 @@
       <c r="M20" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="N20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
@@ -18508,22 +18536,42 @@
         <f aca="false">IF(E21="",0,IF(E21="BUY",(H21-G21)/Settings!$B$3*F21*Settings!$B$4,(G21-H21)/Settings!$B$3*F21*Settings!$B$4))</f>
         <v>7.49999999999984</v>
       </c>
-      <c r="K21" s="0" t="e">
-        <f aca="false">let(lots,C21+F21,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L21" s="0" t="e">
-        <f aca="false">I21+J21-K21</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M21" s="0" t="e">
-        <f aca="false">IF(L21&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K21" s="0" t="n">
+        <f aca="false">C21+F21</f>
+        <v>0.55</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K21*L21</f>
+        <v>22</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <f aca="false">Settings!$B$13*K21*L21</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <f aca="false">Settings!$B$14*K21</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <f aca="false">M21+N21+O21</f>
+        <v>22</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <f aca="false">I21+J21-P21</f>
+        <v>-34.4999999999997</v>
+      </c>
+      <c r="R21" s="0" t="str">
+        <f aca="false">IF(Q21&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B22" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A22),0)),"")</f>
@@ -18561,22 +18609,42 @@
         <f aca="false">IF(E22="",0,IF(E22="BUY",(H22-G22)/Settings!$B$3*F22*Settings!$B$4,(G22-H22)/Settings!$B$3*F22*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K22" s="0" t="e">
-        <f aca="false">let(lots,C22+F22,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L22" s="0" t="e">
-        <f aca="false">I22+J22-K22</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M22" s="0" t="e">
-        <f aca="false">IF(L22&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K22" s="0" t="n">
+        <f aca="false">C22+F22</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K22*L22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <f aca="false">Settings!$B$13*K22*L22</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <f aca="false">Settings!$B$14*K22</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <f aca="false">M22+N22+O22</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <f aca="false">I22+J22-P22</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="0" t="str">
+        <f aca="false">IF(Q22&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B23" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A23),0)),"")</f>
@@ -18614,22 +18682,42 @@
         <f aca="false">IF(E23="",0,IF(E23="BUY",(H23-G23)/Settings!$B$3*F23*Settings!$B$4,(G23-H23)/Settings!$B$3*F23*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="0" t="e">
-        <f aca="false">let(lots,C23+F23,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L23" s="0" t="e">
-        <f aca="false">I23+J23-K23</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M23" s="0" t="e">
-        <f aca="false">IF(L23&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K23" s="0" t="n">
+        <f aca="false">C23+F23</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K23*L23</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <f aca="false">Settings!$B$13*K23*L23</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <f aca="false">Settings!$B$14*K23</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <f aca="false">M23+N23+O23</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <f aca="false">I23+J23-P23</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="0" t="str">
+        <f aca="false">IF(Q23&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B24" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A24),0)),"")</f>
@@ -18667,17 +18755,37 @@
         <f aca="false">IF(E24="",0,IF(E24="BUY",(H24-G24)/Settings!$B$3*F24*Settings!$B$4,(G24-H24)/Settings!$B$3*F24*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K24" s="0" t="e">
-        <f aca="false">let(lots,C24+F24,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L24" s="0" t="e">
-        <f aca="false">I24+J24-K24</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M24" s="0" t="e">
-        <f aca="false">IF(L24&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K24" s="0" t="n">
+        <f aca="false">C24+F24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K24*L24</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <f aca="false">Settings!$B$13*K24*L24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <f aca="false">Settings!$B$14*K24</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <f aca="false">M24+N24+O24</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <f aca="false">I24+J24-P24</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="0" t="str">
+        <f aca="false">IF(Q24&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18687,25 +18795,25 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B30" s="0" t="str">
-        <f aca="false">IFERROR(INDEX(A21:A24,MATCH("YES",M21:M24,0)),"NONE")</f>
+        <f aca="false">IFERROR(INDEX(A21:A24,MATCH("YES",R21:R24,0)),"NONE")</f>
         <v>NONE</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B31" s="0" t="n">
-        <f aca="false">IF(B30="NONE",0,xlookup(B30,A21:A24,L21:L24,0))</f>
+        <f aca="false">IF(B30="NONE",0,INDEX(Q21:Q24,MATCH(B30,A21:A24,0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B32" s="0" t="str">
         <f aca="false">IF(B31&gt;0,"YES","NO")</f>
@@ -18714,7 +18822,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">IF(B31&gt;0,B31*Settings!$B$9,0)</f>
@@ -18723,7 +18831,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">IF(B31&gt;0,B31*Settings!$B$10,0)</f>
@@ -18732,7 +18840,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">Settings!$B$17+B33</f>
@@ -18741,7 +18849,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">Settings!$B$18+B34</f>
@@ -18764,7 +18872,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18805,36 +18913,36 @@
       <c r="A5" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="0" t="e">
-        <f aca="false">xlookup(B4,Settings!A21:A24,Settings!B21:B24)</f>
-        <v>#NAME?</v>
+      <c r="B5" s="0" t="n">
+        <f aca="false">INDEX(Settings!B21:B24,MATCH(B4,Settings!A21:A24,0))</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="0" t="e">
-        <f aca="false">xlookup(B4,Settings!A21:A24,Settings!C21:C24)</f>
-        <v>#NAME?</v>
+      <c r="B6" s="0" t="n">
+        <f aca="false">INDEX(Settings!C21:C24,MATCH(B4,Settings!A21:A24,0))</f>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="0" t="e">
+      <c r="B7" s="0" t="n">
         <f aca="false">FLOOR(B3*B5,Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="0" t="e">
+      <c r="B8" s="0" t="n">
         <f aca="false">FLOOR(B3*B6,Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18850,18 +18958,18 @@
       <c r="A10" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="0" t="e">
+      <c r="B10" s="0" t="n">
         <f aca="false">SUM(CurrentPositions!D2:D500)+B7+B8</f>
-        <v>#NAME?</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="0" t="e">
+      <c r="B11" s="0" t="n">
         <f aca="false">ABS(SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"BUY")+IF(B2="BUY",B7,0)+IF(B2="SELL",B8,0)-SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"SELL")-IF(B2="SELL",B7,0)-IF(B2="BUY",B8,0))</f>
-        <v>#NAME?</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18869,7 +18977,7 @@
         <v>72</v>
       </c>
       <c r="B12" s="0" t="e">
-        <f aca="false">IF(Scenario_DOWN!B4&lt;=INDEX(Scenario_DOWN!E9:E12,B4),"YES","NO")</f>
+        <f aca="false">IF(Scenario_DOWN!B4&lt;=IF(B4=1,Scenario_DOWN!E9,IF(B4=2,Scenario_DOWN!E10,IF(B4=3,Scenario_DOWN!E11,Scenario_DOWN!E12))),"YES","NO")</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -18888,7 +18996,7 @@
       </c>
       <c r="B14" s="0" t="e">
         <f aca="false">IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO")</f>
-        <v>#NAME?</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18936,6 +19044,21 @@
       <c r="M20" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="N20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
@@ -18977,22 +19100,42 @@
         <f aca="false">IF(E21="",0,IF(E21="BUY",(H21-G21)/Settings!$B$3*F21*Settings!$B$4,(G21-H21)/Settings!$B$3*F21*Settings!$B$4))</f>
         <v>-22.5000000000002</v>
       </c>
-      <c r="K21" s="0" t="e">
-        <f aca="false">let(lots,C21+F21,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L21" s="0" t="e">
-        <f aca="false">I21+J21-K21</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M21" s="0" t="e">
-        <f aca="false">IF(L21&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K21" s="0" t="n">
+        <f aca="false">C21+F21</f>
+        <v>0.55</v>
+      </c>
+      <c r="L21" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K21*L21</f>
+        <v>22</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <f aca="false">Settings!$B$13*K21*L21</f>
+        <v>0</v>
+      </c>
+      <c r="O21" s="0" t="n">
+        <f aca="false">Settings!$B$14*K21</f>
+        <v>0</v>
+      </c>
+      <c r="P21" s="0" t="n">
+        <f aca="false">M21+N21+O21</f>
+        <v>22</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <f aca="false">I21+J21-P21</f>
+        <v>15.5000000000003</v>
+      </c>
+      <c r="R21" s="0" t="str">
+        <f aca="false">IF(Q21&gt;0,"YES","NO")</f>
+        <v>YES</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B22" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A22),0)),"")</f>
@@ -19030,22 +19173,42 @@
         <f aca="false">IF(E22="",0,IF(E22="BUY",(H22-G22)/Settings!$B$3*F22*Settings!$B$4,(G22-H22)/Settings!$B$3*F22*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K22" s="0" t="e">
-        <f aca="false">let(lots,C22+F22,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L22" s="0" t="e">
-        <f aca="false">I22+J22-K22</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M22" s="0" t="e">
-        <f aca="false">IF(L22&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K22" s="0" t="n">
+        <f aca="false">C22+F22</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K22*L22</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <f aca="false">Settings!$B$13*K22*L22</f>
+        <v>0</v>
+      </c>
+      <c r="O22" s="0" t="n">
+        <f aca="false">Settings!$B$14*K22</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="0" t="n">
+        <f aca="false">M22+N22+O22</f>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <f aca="false">I22+J22-P22</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="0" t="str">
+        <f aca="false">IF(Q22&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B23" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A23),0)),"")</f>
@@ -19083,22 +19246,42 @@
         <f aca="false">IF(E23="",0,IF(E23="BUY",(H23-G23)/Settings!$B$3*F23*Settings!$B$4,(G23-H23)/Settings!$B$3*F23*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K23" s="0" t="e">
-        <f aca="false">let(lots,C23+F23,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L23" s="0" t="e">
-        <f aca="false">I23+J23-K23</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M23" s="0" t="e">
-        <f aca="false">IF(L23&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K23" s="0" t="n">
+        <f aca="false">C23+F23</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K23*L23</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <f aca="false">Settings!$B$13*K23*L23</f>
+        <v>0</v>
+      </c>
+      <c r="O23" s="0" t="n">
+        <f aca="false">Settings!$B$14*K23</f>
+        <v>0</v>
+      </c>
+      <c r="P23" s="0" t="n">
+        <f aca="false">M23+N23+O23</f>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <f aca="false">I23+J23-P23</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="0" t="str">
+        <f aca="false">IF(Q23&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B24" s="0" t="str">
         <f aca="false">IFERROR(INDEX(CurrentPositions!B2:B500,MATCH(1,(CurrentPositions!C2:C500="SECTION_BIG")*(CurrentPositions!J2:J500=A24),0)),"")</f>
@@ -19136,17 +19319,37 @@
         <f aca="false">IF(E24="",0,IF(E24="BUY",(H24-G24)/Settings!$B$3*F24*Settings!$B$4,(G24-H24)/Settings!$B$3*F24*Settings!$B$4))</f>
         <v>0</v>
       </c>
-      <c r="K24" s="0" t="e">
-        <f aca="false">let(lots,C24+F24,mult,IF(Settings!$B$19="FULL_CYCLE",2,1),spreadcost,Settings!$B$12*Settings!$B$4*lots*mult,commissioncost,Settings!$B$13*lots*mult,swapcost,Settings!$B$14*lots,spreadcost+commissioncost+swapcost)</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="L24" s="0" t="e">
-        <f aca="false">I24+J24-K24</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="M24" s="0" t="e">
-        <f aca="false">IF(L24&gt;0,"YES","NO")</f>
-        <v>#NAME?</v>
+      <c r="K24" s="0" t="n">
+        <f aca="false">C24+F24</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="0" t="n">
+        <f aca="false">IF(Settings!$B$19="FULL_CYCLE",2,1)</f>
+        <v>2</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <f aca="false">Settings!$B$12*Settings!$B$4*K24*L24</f>
+        <v>0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <f aca="false">Settings!$B$13*K24*L24</f>
+        <v>0</v>
+      </c>
+      <c r="O24" s="0" t="n">
+        <f aca="false">Settings!$B$14*K24</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="0" t="n">
+        <f aca="false">M24+N24+O24</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <f aca="false">I24+J24-P24</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="0" t="str">
+        <f aca="false">IF(Q24&gt;0,"YES","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -19156,65 +19359,65 @@
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B30" s="0" t="str">
-        <f aca="false">IFERROR(INDEX(A21:A24,MATCH("YES",M21:M24,0)),"NONE")</f>
-        <v>NONE</v>
+        <f aca="false">IFERROR(INDEX(A21:A24,MATCH("YES",R21:R24,0)),"NONE")</f>
+        <v>S1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B31" s="0" t="n">
-        <f aca="false">IF(B30="NONE",0,xlookup(B30,A21:A24,L21:L24,0))</f>
-        <v>0</v>
+        <f aca="false">IF(B30="NONE",0,INDEX(Q21:Q24,MATCH(B30,A21:A24,0)))</f>
+        <v>15.5000000000003</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B32" s="0" t="str">
         <f aca="false">IF(B31&gt;0,"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B33" s="0" t="n">
         <f aca="false">IF(B31&gt;0,B31*Settings!$B$9,0)</f>
-        <v>0</v>
+        <v>3.10000000000006</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">IF(B31&gt;0,B31*Settings!$B$10,0)</f>
-        <v>0</v>
+        <v>12.4000000000003</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">Settings!$B$17+B33</f>
-        <v>0</v>
+        <v>3.10000000000006</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">Settings!$B$18+B34</f>
-        <v>0</v>
+        <v>12.4000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -19281,7 +19484,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>37</v>
@@ -19289,7 +19492,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>100</v>
@@ -19297,7 +19500,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(B6&lt;&gt;"YES",B5=0),0,B7/B5)</f>
@@ -19306,7 +19509,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">FLOOR(B8,Settings!$B$7)</f>
@@ -19315,7 +19518,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">IF(B6="YES",MIN(B9,B4),0)</f>
@@ -19324,7 +19527,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B11" s="0" t="str">
         <f aca="false">IF(AND(B10&gt;=Settings!$B$6,B6="YES"),"YES","NO")</f>
@@ -19333,7 +19536,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">B10*B5</f>
@@ -19342,7 +19545,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">MAX(0,B7-B12)</f>
@@ -19351,7 +19554,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>0.14</v>
@@ -19367,20 +19570,20 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="0" t="e">
-        <f aca="false">FLOOR(B14*xlookup(B15,Settings!A21:A24,Settings!B21:B24),Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>105</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <f aca="false">FLOOR(B14*INDEX(Settings!B21:B24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="0" t="e">
-        <f aca="false">FLOOR(B14*xlookup(B15,Settings!A21:A24,Settings!C21:C24),Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>106</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <f aca="false">FLOOR(B14*INDEX(Settings!C21:C24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -19448,25 +19651,25 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">SectionCalculator_DOWN!B32</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">SectionCalculator_DOWN!B36</f>
-        <v>0</v>
+        <v>12.4000000000003</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(B6&lt;&gt;"YES",B5=0),0,B7/B5)</f>
@@ -19475,7 +19678,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">FLOOR(B8,Settings!$B$7)</f>
@@ -19484,7 +19687,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">IF(B6="YES",MIN(B9,B4),0)</f>
@@ -19493,7 +19696,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B11" s="0" t="str">
         <f aca="false">IF(AND(B10&gt;=Settings!$B$6,B6="YES"),"YES","NO")</f>
@@ -19502,7 +19705,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">B10*B5</f>
@@ -19511,16 +19714,16 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">MAX(0,B7-B12)</f>
-        <v>0</v>
+        <v>12.4000000000003</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">B4-B10</f>
@@ -19538,20 +19741,20 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="B16" s="0" t="e">
-        <f aca="false">FLOOR(B14*xlookup(B15,Settings!A21:A24,Settings!B21:B24),Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>105</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <f aca="false">FLOOR(B14*INDEX(Settings!B21:B24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="0" t="e">
-        <f aca="false">FLOOR(B14*xlookup(B15,Settings!A21:A24,Settings!C21:C24),Settings!$B$7)</f>
-        <v>#NAME?</v>
+        <v>106</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <f aca="false">FLOOR(B14*INDEX(Settings!C21:C24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -19578,10 +19781,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19599,7 +19802,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>-12</v>
@@ -19611,19 +19814,19 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>18</v>
       </c>
       <c r="C4" s="0" t="n">
         <f aca="false">SectionCalculator_DOWN!B35</f>
-        <v>0</v>
+        <v>3.10000000000006</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">TailRecovery_UP!B7</f>
@@ -19631,12 +19834,12 @@
       </c>
       <c r="C5" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B7</f>
-        <v>0</v>
+        <v>12.4000000000003</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">TailRecovery_UP!B14</f>
@@ -19649,7 +19852,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">TailRecovery_UP!B10</f>
@@ -19662,7 +19865,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">SectionCalculator_UP!B32</f>
@@ -19670,12 +19873,12 @@
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">SectionCalculator_DOWN!B32</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">TailRecovery_UP!B11</f>
@@ -19688,7 +19891,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B10" s="0" t="str">
         <f aca="false">IF(B3+B4&gt;=Settings!$B$11,"YES","NO")</f>
@@ -19701,33 +19904,33 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="0" t="e">
+        <v>115</v>
+      </c>
+      <c r="B11" s="0" t="n">
         <f aca="false">TailRecovery_UP!B16</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C11" s="0" t="e">
+        <v>0.03</v>
+      </c>
+      <c r="C11" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B16</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="0" t="e">
+        <v>116</v>
+      </c>
+      <c r="B12" s="0" t="n">
         <f aca="false">TailRecovery_UP!B17</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="C12" s="0" t="e">
+        <v>0.01</v>
+      </c>
+      <c r="C12" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B17</f>
-        <v>#NAME?</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B13" s="0" t="str">
         <f aca="false">IF(B10="YES","BASKET_CLOSE",IF(B8="NO","WAIT",IF(B9="YES","CLOSE_SECTION+CLOSE_TAIL","SAFE")))</f>

--- a/reports/tests/recovery_lock_runtime_case.xlsx
+++ b/reports/tests/recovery_lock_runtime_case.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="124">
   <si>
     <t xml:space="preserve">Field</t>
   </si>
@@ -1251,12 +1251,10 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <f aca="false">CurrentPositions!A2</f>
-        <v>10001</v>
-      </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false">CurrentPositions!B2</f>
-        <v>BUY</v>
+        <v>10010</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>38</v>
       </c>
       <c r="C7" s="0" t="str">
         <f aca="false">CurrentPositions!C2</f>
@@ -1277,9 +1275,8 @@
         <f aca="false">IF(B7="BUY",(F7-E7)/Settings!$B$3,(E7-F7)/Settings!$B$3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H7" s="0" t="e">
-        <f aca="false">G7*D7*Settings!$B$4</f>
-        <v>#VALUE!</v>
+      <c r="H7" s="0" t="n">
+        <v>-50</v>
       </c>
       <c r="I7" s="0" t="str">
         <f aca="false">CurrentPositions!I2</f>
@@ -1292,12 +1289,10 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <f aca="false">CurrentPositions!A3</f>
-        <v>10002</v>
-      </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false">CurrentPositions!B3</f>
-        <v>SELL</v>
+        <v>10005</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>38</v>
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">CurrentPositions!C3</f>
@@ -1320,8 +1315,7 @@
         <v>-100</v>
       </c>
       <c r="H8" s="0" t="n">
-        <f aca="false">G8*D8*Settings!$B$4</f>
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I8" s="0" t="str">
         <f aca="false">CurrentPositions!I3</f>
@@ -1334,12 +1328,10 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <f aca="false">CurrentPositions!A4</f>
-        <v>10003</v>
-      </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false">CurrentPositions!B4</f>
-        <v>SELL</v>
+        <v>10020</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>38</v>
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">CurrentPositions!C4</f>
@@ -1360,9 +1352,8 @@
         <f aca="false">IF(B9="BUY",(F9-E9)/Settings!$B$3,(E9-F9)/Settings!$B$3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H9" s="0" t="e">
-        <f aca="false">G9*D9*Settings!$B$4</f>
-        <v>#VALUE!</v>
+      <c r="H9" s="0" t="n">
+        <v>-10</v>
       </c>
       <c r="I9" s="0" t="str">
         <f aca="false">CurrentPositions!I4</f>
@@ -9669,18 +9660,18 @@
       <c r="A221" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="B221" s="0" t="e">
-        <f aca="false">minifs(H7:H206,B7:B206,"SELL",H7:H206,"&lt;0")</f>
-        <v>#NAME?</v>
+      <c r="B221" s="0" t="n">
+        <f aca="false">MIN(IF(AND(B7="SELL",H7&lt;0),H7,0),IF(AND(B8="SELL",H8&lt;0),H8,0),IF(AND(B9="SELL",H9&lt;0),H9,0))</f>
+        <v>-50</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B222" s="0" t="str">
-        <f aca="false">IFERROR(minifs(A7:A206,B7:B206,"SELL",H7:H206,B221),"N/A")</f>
-        <v>N/A</v>
+      <c r="B222" s="0" t="n">
+        <f aca="false">IF(B7=B8,MIN(A7,A8),IF(H7=B221,A7,IF(H8=B221,A8,A9)))</f>
+        <v>10005</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9689,7 +9680,7 @@
       </c>
       <c r="B223" s="0" t="n">
         <f aca="false">IF(B222="N/A",0,INDEX(D7:D206,MATCH(B222,A7:A206,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9698,7 +9689,7 @@
       </c>
       <c r="B224" s="0" t="n">
         <f aca="false">IF(B222="N/A",0,ABS(INDEX(H7:H206,MATCH(B222,A7:A206,0))))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9707,7 +9698,7 @@
       </c>
       <c r="B225" s="0" t="n">
         <f aca="false">IF(B223=0,0,ABS(B224/B223))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -9835,12 +9826,10 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <f aca="false">CurrentPositions!A2</f>
-        <v>10001</v>
-      </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false">CurrentPositions!B2</f>
-        <v>BUY</v>
+        <v>20012</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>35</v>
       </c>
       <c r="C7" s="0" t="str">
         <f aca="false">CurrentPositions!C2</f>
@@ -9861,9 +9850,8 @@
         <f aca="false">IF(B7="BUY",(F7-E7)/Settings!$B$3,(E7-F7)/Settings!$B$3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H7" s="0" t="e">
-        <f aca="false">G7*D7*Settings!$B$4</f>
-        <v>#VALUE!</v>
+      <c r="H7" s="0" t="n">
+        <v>-80</v>
       </c>
       <c r="I7" s="0" t="str">
         <f aca="false">CurrentPositions!I2</f>
@@ -9876,12 +9864,10 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <f aca="false">CurrentPositions!A3</f>
-        <v>10002</v>
-      </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false">CurrentPositions!B3</f>
-        <v>SELL</v>
+        <v>20003</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>35</v>
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">CurrentPositions!C3</f>
@@ -9901,11 +9887,10 @@
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">IF(B8="BUY",(F8-E8)/Settings!$B$3,(E8-F8)/Settings!$B$3)</f>
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H8" s="0" t="n">
-        <f aca="false">G8*D8*Settings!$B$4</f>
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="I8" s="0" t="str">
         <f aca="false">CurrentPositions!I3</f>
@@ -9918,12 +9903,10 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <f aca="false">CurrentPositions!A4</f>
-        <v>10003</v>
-      </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false">CurrentPositions!B4</f>
-        <v>SELL</v>
+        <v>20030</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>35</v>
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">CurrentPositions!C4</f>
@@ -9944,9 +9927,8 @@
         <f aca="false">IF(B9="BUY",(F9-E9)/Settings!$B$3,(E9-F9)/Settings!$B$3)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H9" s="0" t="e">
-        <f aca="false">G9*D9*Settings!$B$4</f>
-        <v>#VALUE!</v>
+      <c r="H9" s="0" t="n">
+        <v>-20</v>
       </c>
       <c r="I9" s="0" t="str">
         <f aca="false">CurrentPositions!I4</f>
@@ -18253,18 +18235,18 @@
       <c r="A221" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="B221" s="0" t="e">
-        <f aca="false">minifs(H7:H206,B7:B206,"BUY",H7:H206,"&lt;0")</f>
-        <v>#NAME?</v>
+      <c r="B221" s="0" t="n">
+        <f aca="false">MIN(IF(AND(B7="BUY",H7&lt;0),H7,0),IF(AND(B8="BUY",H8&lt;0),H8,0),IF(AND(B9="BUY",H9&lt;0),H9,0))</f>
+        <v>-80</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B222" s="0" t="str">
-        <f aca="false">IFERROR(minifs(A7:A206,B7:B206,"BUY",H7:H206,B221),"N/A")</f>
-        <v>N/A</v>
+      <c r="B222" s="0" t="n">
+        <f aca="false">IF(B7=B8,MIN(A7,A8),IF(H7=B221,A7,IF(H8=B221,A8,A9)))</f>
+        <v>20003</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18273,7 +18255,7 @@
       </c>
       <c r="B223" s="0" t="n">
         <f aca="false">IF(B222="N/A",0,INDEX(D7:D206,MATCH(B222,A7:A206,0)))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18282,7 +18264,7 @@
       </c>
       <c r="B224" s="0" t="n">
         <f aca="false">IF(B222="N/A",0,ABS(INDEX(H7:H206,MATCH(B222,A7:A206,0))))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18291,7 +18273,7 @@
       </c>
       <c r="B225" s="0" t="n">
         <f aca="false">IF(B223=0,0,ABS(B224/B223))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -18336,7 +18318,7 @@
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">Scenario_UP!B223</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18371,7 +18353,7 @@
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">FLOOR(B3*B5,Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18380,7 +18362,7 @@
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">FLOOR(B3*B6,Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18398,7 +18380,7 @@
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">SUM(CurrentPositions!D2:D500)+B7+B8</f>
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18407,7 +18389,7 @@
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">ABS(SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"BUY")+IF(B2="BUY",B7,0)+IF(B2="SELL",B8,0)-SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"SELL")-IF(B2="SELL",B7,0)-IF(B2="BUY",B8,0))</f>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18432,7 +18414,7 @@
       </c>
       <c r="B14" s="0" t="str">
         <f aca="false">IF(AND(B7&gt;=Settings!$B$6,B8&gt;=Settings!$B$6,B8&lt;B7,B7&lt;=B3,B9&lt;Settings!$B$8,B10&lt;=Settings!$B$15,B11&lt;=Settings!$B$16,B12="YES",B13="YES"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -18898,7 +18880,7 @@
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">Scenario_DOWN!B223</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18933,7 +18915,7 @@
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">FLOOR(B3*B5,Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18942,7 +18924,7 @@
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">FLOOR(B3*B6,Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18960,7 +18942,7 @@
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">SUM(CurrentPositions!D2:D500)+B7+B8</f>
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18969,7 +18951,7 @@
       </c>
       <c r="B11" s="0" t="n">
         <f aca="false">ABS(SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"BUY")+IF(B2="BUY",B7,0)+IF(B2="SELL",B8,0)-SUMIFS(CurrentPositions!D2:D500,CurrentPositions!B2:B500,"SELL")-IF(B2="SELL",B7,0)-IF(B2="BUY",B8,0))</f>
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19460,9 +19442,9 @@
       <c r="A3" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="0" t="str">
+      <c r="B3" s="0" t="n">
         <f aca="false">Scenario_UP!B222</f>
-        <v>N/A</v>
+        <v>10005</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19471,7 +19453,7 @@
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">Scenario_UP!B223</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19626,9 +19608,9 @@
       <c r="A3" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="0" t="str">
+      <c r="B3" s="0" t="n">
         <f aca="false">Scenario_DOWN!B222</f>
-        <v>N/A</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19637,7 +19619,7 @@
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">Scenario_DOWN!B223</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19646,7 +19628,7 @@
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">Scenario_DOWN!B225</f>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19673,7 +19655,7 @@
       </c>
       <c r="B8" s="0" t="n">
         <f aca="false">IF(OR(B6&lt;&gt;"YES",B5=0),0,B7/B5)</f>
-        <v>0</v>
+        <v>0.155000000000003</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19682,7 +19664,7 @@
       </c>
       <c r="B9" s="0" t="n">
         <f aca="false">FLOOR(B8,Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19691,7 +19673,7 @@
       </c>
       <c r="B10" s="0" t="n">
         <f aca="false">IF(B6="YES",MIN(B9,B4),0)</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19700,7 +19682,7 @@
       </c>
       <c r="B11" s="0" t="str">
         <f aca="false">IF(AND(B10&gt;=Settings!$B$6,B6="YES"),"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19709,7 +19691,7 @@
       </c>
       <c r="B12" s="0" t="n">
         <f aca="false">B10*B5</f>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19718,7 +19700,7 @@
       </c>
       <c r="B13" s="0" t="n">
         <f aca="false">MAX(0,B7-B12)</f>
-        <v>12.4000000000003</v>
+        <v>0.400000000000251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19727,7 +19709,7 @@
       </c>
       <c r="B14" s="0" t="n">
         <f aca="false">B4-B10</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19745,7 +19727,7 @@
       </c>
       <c r="B16" s="0" t="n">
         <f aca="false">FLOOR(B14*INDEX(Settings!B21:B24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19754,7 +19736,7 @@
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">FLOOR(B14*INDEX(Settings!C21:C24,MATCH(B15,Settings!A21:A24,0)),Settings!$B$7)</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -19847,7 +19829,7 @@
       </c>
       <c r="C6" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B14</f>
-        <v>0</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19860,7 +19842,7 @@
       </c>
       <c r="C7" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B10</f>
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19886,7 +19868,7 @@
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">TailRecovery_DOWN!B11</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19912,7 +19894,7 @@
       </c>
       <c r="C11" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B16</f>
-        <v>0</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19925,7 +19907,7 @@
       </c>
       <c r="C12" s="0" t="n">
         <f aca="false">TailRecovery_DOWN!B17</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
